--- a/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/cyber_risks.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/cyber_risks.xlsx
@@ -479,17 +479,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Third-party</t>
+          <t>Cloud misconfig</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -501,17 +501,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ransomware</t>
+          <t>Data exfil</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Accepted</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Accepted</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ransomware</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mitigating</t>
+          <t>Accepted</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ransomware</t>
+          <t>Data exfil</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mitigating</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ransomware</t>
+          <t>Third-party</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Phishing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Mitigating</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cloud misconfig</t>
+          <t>Third-party</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data exfil</t>
+          <t>Cloud misconfig</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mitigating</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Ransomware</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Mitigating</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cloud misconfig</t>
+          <t>Third-party</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,17 +743,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Phishing</t>
+          <t>Cloud misconfig</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Mitigating</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Accepted</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Phishing</t>
+          <t>Data exfil</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Third-party</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Accepted</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Data exfil</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Mitigating</t>
         </is>
       </c>
     </row>
@@ -875,17 +875,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cloud misconfig</t>
+          <t>Phishing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Phishing</t>
+          <t>Data exfil</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mitigating</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
